--- a/output/tables/mesh/experiment_1/stats-level_glm_level0.xlsx
+++ b/output/tables/mesh/experiment_1/stats-level_glm_level0.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>mesh_term</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>stats.sign</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -409,6 +414,11 @@
           <t>Organisms</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -433,6 +443,11 @@
           <t>Analytical, Diagnostic and Therapeutic Techniques, and Equipment</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -457,6 +472,11 @@
           <t>Health Care</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -481,6 +501,11 @@
           <t>Phenomena and Processes</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -505,6 +530,11 @@
           <t>Information Science</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +559,11 @@
           <t>Diseases</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +588,11 @@
           <t>Named Groups</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +617,11 @@
           <t>Psychiatry and Psychology</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -601,6 +646,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -625,6 +675,11 @@
           <t>Anatomy</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -649,6 +704,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,6 +733,11 @@
           <t>Chemicals and Drugs</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -697,6 +762,11 @@
           <t>Disciplines and Occupations</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -721,6 +791,11 @@
           <t>Anthropology, Education, Sociology, and Social Phenomena</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -745,6 +820,11 @@
           <t>Geographicals</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -769,6 +849,11 @@
           <t>Technology, Industry, and Agriculture</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -791,6 +876,11 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
